--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260805.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.85%</t>
+          <t>9.88%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.79%</t>
+          <t>8.76%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>6.04%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>109,474,000</t>
+          <t>186,198,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>186,198,000</t>
+          <t>109,474,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -748,112 +748,112 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,030,000</t>
+          <t>27,028,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>26,828,000</t>
+          <t>5,030,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,131</t>
+          <t>430,925,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>424,925,000</t>
+          <t>358,289,964</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>356,289,964</t>
+          <t>2,056</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,88 +865,88 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>131,819,945</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>131,819,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>82,618,000</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>82,618,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>62,540,000</t>
+          <t>63,040,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,617,000</t>
+          <t>28,750,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>28,750,000</t>
+          <t>99,617,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>55,187,000</t>
+          <t>35,720,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>55,187,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>35,720,000</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,650,148,162</t>
+          <t>13,847,535,840</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,946,755,308</t>
+          <t>4,454,107,583</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-153,650,584</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
